--- a/data/trans_orig/P6902-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6902-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>28276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>13197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23397</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>31002</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48511</t>
+          <t>47995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28555</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>23468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40023</t>
+          <t>40461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>39871</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>24491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40035</t>
+          <t>40423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60995</t>
+          <t>61383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32178</t>
+          <t>32526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49578</t>
+          <t>50269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17981</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44089</t>
+          <t>43701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65049</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27051</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>27073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>20734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31288</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45612</t>
+          <t>45774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34322</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29534</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48423</t>
+          <t>48805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t>32224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51495</t>
+          <t>50459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>24931</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>35095</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,42%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32723</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52665</t>
+          <t>52249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27634</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>52107</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73521</t>
+          <t>75327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>57,07%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>36199</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55725</t>
+          <t>56485</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58462</t>
+          <t>56656</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80771</t>
+          <t>79876</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,52%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>34307</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54106</t>
+          <t>54875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28401</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53646</t>
+          <t>53239</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79871</t>
+          <t>78130</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54809</t>
+          <t>54040</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74914</t>
+          <t>74608</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21385</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>35086</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>78830</t>
+          <t>80571</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>105055</t>
+          <t>105462</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,45%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>182842</t>
+          <t>185412</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>226766</t>
+          <t>229307</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99095</t>
+          <t>97668</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>129325</t>
+          <t>126680</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>292085</t>
+          <t>292908</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>345489</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>245539</t>
+          <t>242998</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>289463</t>
+          <t>286893</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90796</t>
+          <t>93441</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>121026</t>
+          <t>122453</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>348448</t>
+          <t>346938</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>400342</t>
+          <t>399519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>15646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28189</t>
+          <t>27929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>20994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>29126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>39982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55098</t>
+          <t>55146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>22462</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>28271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>35620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>22309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34850</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53528</t>
+          <t>55603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>36820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24012</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37377</t>
+          <t>35302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23587</t>
+          <t>23125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32567</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>17577</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>31299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11775</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>23372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>51289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28564</t>
+          <t>28427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17760</t>
+          <t>16820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>24251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>41354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>12756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23591</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>28141</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>21647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36610</t>
+          <t>36094</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36881</t>
+          <t>36917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,04%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25383</t>
+          <t>24789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40530</t>
+          <t>39713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>33095</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49036</t>
+          <t>48708</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68281</t>
+          <t>68848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29047</t>
+          <t>29641</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26821</t>
+          <t>26690</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32529</t>
+          <t>31962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51774</t>
+          <t>52102</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>21572</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>19446</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37372</t>
+          <t>37628</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23547</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>35872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23091</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>38163</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56221</t>
+          <t>56345</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>133156</t>
+          <t>134651</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>170842</t>
+          <t>170371</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>108010</t>
+          <t>107731</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>138217</t>
+          <t>138490</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>252559</t>
+          <t>251828</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>300396</t>
+          <t>299706</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>154263</t>
+          <t>154734</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>191949</t>
+          <t>190454</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>77611</t>
+          <t>77338</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107818</t>
+          <t>108097</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>240537</t>
+          <t>241227</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>289105</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23363</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39957</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31845</t>
+          <t>31596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49195</t>
+          <t>47956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67867</t>
+          <t>68852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35214</t>
+          <t>34103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>22121</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50266</t>
+          <t>51505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31880</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>19945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>32327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36632</t>
+          <t>37443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59593</t>
+          <t>61894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50906</t>
+          <t>51012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67466</t>
+          <t>68028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22770</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65890</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88851</t>
+          <t>88040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,16%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20316</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20694</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30143</t>
+          <t>30167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18988</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>29002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>23909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35322</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51055</t>
+          <t>51205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27078</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>18740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>19570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22895</t>
+          <t>23069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41561</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>28763</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43982</t>
+          <t>44057</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55411</t>
+          <t>57577</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80816</t>
+          <t>80740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36781</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55447</t>
+          <t>55273</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25818</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53208</t>
+          <t>53284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78613</t>
+          <t>76447</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>57,04%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>26630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37475</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25189</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>38909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132290</t>
+          <t>132941</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>170699</t>
+          <t>171739</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>115947</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>145027</t>
+          <t>144767</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>256966</t>
+          <t>258995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>307060</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>179302</t>
+          <t>178262</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>217711</t>
+          <t>217060</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>71271</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>100351</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>259239</t>
+          <t>258428</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>309333</t>
+          <t>307304</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26052</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>29927</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>31293</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36189</t>
+          <t>35923</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56479</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33738</t>
+          <t>33243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>26073</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35244</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55534</t>
+          <t>55800</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,83%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30530</t>
+          <t>30437</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>33676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>44481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60452</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32599</t>
+          <t>32585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22738</t>
+          <t>23298</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52275</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23387</t>
+          <t>22379</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37640</t>
+          <t>37298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64224</t>
+          <t>65381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31137</t>
+          <t>31810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97070</t>
+          <t>96953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16966</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16428</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67815</t>
+          <t>68213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89868</t>
+          <t>89195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>22564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,5%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>25320</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38293</t>
+          <t>39245</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18705</t>
+          <t>19215</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>36511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40180</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56998</t>
+          <t>57128</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>46631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>58524</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91426</t>
+          <t>90837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111658</t>
+          <t>111820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>16050</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>32825</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52279</t>
+          <t>52868</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37667</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50700</t>
+          <t>50567</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27389</t>
+          <t>25526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46282</t>
+          <t>45957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70711</t>
+          <t>70350</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93536</t>
+          <t>93283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>18656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27321</t>
+          <t>29184</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>41117</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>191466</t>
+          <t>190398</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>227618</t>
+          <t>227815</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>149821</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>243927</t>
+          <t>241655</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>354902</t>
+          <t>349388</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>460070</t>
+          <t>456275</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>111887</t>
+          <t>111690</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>148039</t>
+          <t>149107</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>110288</t>
+          <t>112560</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>204394</t>
+          <t>202758</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>233650</t>
+          <t>237445</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>338818</t>
+          <t>344332</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
